--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:51</t>
+          <t>2026-05-05 20:19</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Customer_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer_Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer_Summary'!$A$4:$F$11</definedName>
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:19</t>
+          <t>2026-05-08 15:11</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>811000</v>
+        <v>808500</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>7500</v>
+        <v>3750</v>
       </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>164500</v>
+        <v>163500</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1013000</v>
+        <v>1005750</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>808500</v>
+        <v>733061</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>163500</v>
+        <v>147134</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>30000</v>
+        <v>26000</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1005750</v>
+        <v>909445</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -104,13 +104,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>733061</v>
+        <v>735782.46</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3250</v>
+        <v>3273.09</v>
       </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>147134</v>
+        <v>147751</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>909445</v>
+        <v>912806</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>735782.46</v>
+        <v>720918.4</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>147751</v>
+        <v>140319</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>912806</v>
+        <v>890510</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer_Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer_Summary'!$A$4:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer_Summary'!$A$4:$F$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>720918.4</v>
+        <v>713418.4</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -557,16 +557,16 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ในนั้น: เที่ยวเพิ่ม (manual_extra_trips ไม่มีใน GPS)</t>
+          <t>ค่าขนส่งขากลับ (manual_return_trips — ไม่เพิ่มจำนวน matched)</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>7500</v>
+        <v>3273.09</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -575,16 +575,16 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ค่าขนส่งขากลับ (manual_return_trips — ไม่เพิ่มจำนวน matched)</t>
+          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3273.09</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -593,16 +593,16 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
+          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>0</v>
+        <v>140319</v>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -611,16 +611,16 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
+          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>140319</v>
+        <v>26000</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -629,41 +629,23 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
+          <t>Grand (A+C+D+R)</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>26000</v>
+        <v>883010</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Grand (A+C+D+R)</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>890510</v>
-      </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F11"/>
+  <autoFilter ref="A4:F10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Customer_Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Customer_Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer_Summary'!$A$4:$F$10</definedName>
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-06-04 19:42</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>713418.4</v>
+        <v>1158135.79</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>140319</v>
+        <v>278353</v>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>26000</v>
+        <v>14864</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>883010</v>
+        <v>1454625</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:42</t>
+          <t>2026-06-05 14:46</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1158135.79</v>
+        <v>1147055</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3273.09</v>
+        <v>3250</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>278353</v>
+        <v>275659</v>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>14864</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1454625</v>
+        <v>1425964</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1147055</v>
+        <v>1129408</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>275659</v>
+        <v>271408</v>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1425964</v>
+        <v>1404066</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>271408</v>
+        <v>337312</v>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1404066</v>
+        <v>1469970</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>3250</v>
+        <v>32690</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1469970</v>
+        <v>1499410</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Customer_Summary" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer_Summary'!$A$4:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Customer_Summary'!$A$4:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1129408</v>
+        <v>1121952</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -562,11 +562,11 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>ค่าขนส่งขากลับ (manual_return_trips — ไม่เพิ่มจำนวน matched)</t>
+          <t>ค่าขนส่งขากลับ (manual_return_trips kind=backhaul — ไม่เพิ่มจำนวน matched)</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>32690</v>
+        <v>29058</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -575,16 +575,16 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Rd</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
+          <t>ค่าตีเปล่า (manual_return_trips kind=deadhead — ไม่เพิ่มจำนวน matched)</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>11088</v>
       </c>
       <c r="D7" s="5" t="n"/>
       <c r="E7" s="5" t="n"/>
@@ -593,16 +593,16 @@
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
+          <t>ค่าชดเชยเที่ยวขาด (min 2/คัน/วัน) — ไม่เก็บเงิน (ใช้ชาร์จ 50% วันละ 1 เที่ยวแทน)</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>337312</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n"/>
       <c r="E8" s="7" t="n"/>
@@ -611,16 +611,16 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
+          <t>ชาร์จ 50% วันที่วิ่งได้ 1 เที่ยว (หลัง override)</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>337312</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -629,23 +629,41 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Grand (A+C+D+R)</t>
+          <t>No-work recovery outbound 50pct (first matched trip that Dest_In day on recovery dates)</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>1499410</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
     </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Grand (A+C+D+R+Rd)</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>1499410</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F10"/>
+  <autoFilter ref="A4:F11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="C6" s="8" t="n">
-        <v>29058</v>
+        <v>25808</v>
       </c>
       <c r="D6" s="7" t="n"/>
       <c r="E6" s="7" t="n"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1499410</v>
+        <v>1496160</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>1121952</v>
+        <v>1114592</v>
       </c>
       <c r="D5" s="5" t="n"/>
       <c r="E5" s="5" t="n"/>
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>337312</v>
+        <v>333632</v>
       </c>
       <c r="D9" s="5" t="n"/>
       <c r="E9" s="5" t="n"/>
@@ -656,7 +656,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>1496160</v>
+        <v>1485120</v>
       </c>
       <c r="D11" s="5" t="n"/>
       <c r="E11" s="5" t="n"/>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/06_Customer_Summary.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
